--- a/Result/profitability/2486.xlsx
+++ b/Result/profitability/2486.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.51</v>
       </c>
       <c r="M2" t="n">
-        <v>0.125</v>
+        <v>0.21</v>
       </c>
       <c r="N2" t="n">
-        <v>15.98</v>
+        <v>16.655</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.87</v>
       </c>
       <c r="M3" t="n">
-        <v>0.24125</v>
+        <v>0.31375</v>
       </c>
       <c r="N3" t="n">
-        <v>17.30875</v>
+        <v>18.36625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.96</v>
       </c>
       <c r="M4" t="n">
-        <v>0.35625</v>
+        <v>0.4349999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>19.13875</v>
+        <v>19.94625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.14</v>
       </c>
       <c r="M5" t="n">
-        <v>0.34</v>
+        <v>0.42375</v>
       </c>
       <c r="N5" t="n">
-        <v>18.29625</v>
+        <v>19.355</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.44</v>
       </c>
       <c r="M6" t="n">
-        <v>0.40125</v>
+        <v>0.45125</v>
       </c>
       <c r="N6" t="n">
-        <v>18.385</v>
+        <v>19.24625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5387500000000001</v>
+        <v>0.60875</v>
       </c>
       <c r="N7" t="n">
-        <v>19.78375</v>
+        <v>20.4225</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6887500000000001</v>
+        <v>0.73</v>
       </c>
       <c r="N8" t="n">
-        <v>21.03375</v>
+        <v>21.02375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.57</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7462500000000001</v>
+        <v>0.74625</v>
       </c>
       <c r="N10" t="n">
         <v>21.20625</v>
@@ -1899,7 +1899,7 @@
         <v>0.39</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6775000000000001</v>
+        <v>0.6775</v>
       </c>
       <c r="N12" t="n">
         <v>19.4725</v>
@@ -2026,7 +2026,7 @@
         <v>0.24</v>
       </c>
       <c r="M13" t="n">
-        <v>0.725</v>
+        <v>0.7250000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>20.8225</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2486</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2063</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1630</v>
+      </c>
+      <c r="E75" t="n">
+        <v>432</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="G75" t="n">
+        <v>183</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.87%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>177</v>
+      </c>
+      <c r="K75" t="n">
+        <v>146</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.13875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.88125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.137931034482759</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.08000000000000185</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.003800475059382524</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-13.4</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.469999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6776</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
